--- a/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30997</t>
+          <t>31830</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46893</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41510</t>
+          <t>40535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59092</t>
+          <t>59378</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77724</t>
+          <t>78001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101781</t>
+          <t>101065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>57562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74212</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59197</t>
+          <t>58911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>77754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121718</t>
+          <t>122434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145775</t>
+          <t>145498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39436</t>
+          <t>39986</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>56603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49370</t>
+          <t>49753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67402</t>
+          <t>67909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93149</t>
+          <t>93848</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117584</t>
+          <t>119044</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68443</t>
+          <t>68362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85529</t>
+          <t>84979</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73340</t>
+          <t>72833</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91372</t>
+          <t>90989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148123</t>
+          <t>146663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172558</t>
+          <t>171859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37952</t>
+          <t>37639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52775</t>
+          <t>53939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44986</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61601</t>
+          <t>60331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87356</t>
+          <t>86939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110286</t>
+          <t>109781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55073</t>
+          <t>53909</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69896</t>
+          <t>70209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50972</t>
+          <t>52242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67587</t>
+          <t>68006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110134</t>
+          <t>110639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133064</t>
+          <t>133481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56308</t>
+          <t>56927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77528</t>
+          <t>79160</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55642</t>
+          <t>55226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75256</t>
+          <t>75176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116055</t>
+          <t>118548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146256</t>
+          <t>146690</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87808</t>
+          <t>86176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109028</t>
+          <t>108409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81690</t>
+          <t>81770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101304</t>
+          <t>101720</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>176026</t>
+          <t>175592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>206227</t>
+          <t>203734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,22%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182877</t>
+          <t>181145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>216941</t>
+          <t>217000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>208778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243856</t>
+          <t>245146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>401501</t>
+          <t>399580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>451997</t>
+          <t>453282</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>286359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320482</t>
+          <t>322214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>283403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319982</t>
+          <t>319771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>579911</t>
+          <t>578626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>630407</t>
+          <t>632328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>37410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>55236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47052</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64623</t>
+          <t>65466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91083</t>
+          <t>89991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113649</t>
+          <t>113616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,2%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>41893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59190</t>
+          <t>59719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47878</t>
+          <t>47035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>64621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95980</t>
+          <t>96013</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118546</t>
+          <t>119638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,07%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56461</t>
+          <t>57306</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75451</t>
+          <t>75299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67406</t>
+          <t>67637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88260</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130032</t>
+          <t>130428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157692</t>
+          <t>156402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>53684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72522</t>
+          <t>71677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66296</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87150</t>
+          <t>86919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>127137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153507</t>
+          <t>153111</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40562</t>
+          <t>40651</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56890</t>
+          <t>56210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46171</t>
+          <t>46677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64835</t>
+          <t>64233</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90080</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114116</t>
+          <t>114824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47961</t>
+          <t>48641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64289</t>
+          <t>64200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51949</t>
+          <t>52551</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70613</t>
+          <t>70107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>107518</t>
+          <t>106810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131554</t>
+          <t>130500</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52523</t>
+          <t>52606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74273</t>
+          <t>72875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59734</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>80992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117960</t>
+          <t>118683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146438</t>
+          <t>146795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71729</t>
+          <t>73127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93479</t>
+          <t>93396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74845</t>
+          <t>73949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95207</t>
+          <t>95241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154505</t>
+          <t>154148</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182983</t>
+          <t>182260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205564</t>
+          <t>204644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239769</t>
+          <t>239956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239227</t>
+          <t>240217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>276099</t>
+          <t>278303</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>454290</t>
+          <t>454476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>509320</t>
+          <t>506927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>237196</t>
+          <t>237009</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271401</t>
+          <t>272321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>262682</t>
+          <t>260478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>299554</t>
+          <t>298564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>506426</t>
+          <t>508819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>561456</t>
+          <t>561270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39971</t>
+          <t>40284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32911</t>
+          <t>33147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50078</t>
+          <t>51089</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61757</t>
+          <t>61617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>84072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>49801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>65130</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54596</t>
+          <t>53585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71763</t>
+          <t>71527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109225</t>
+          <t>110687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133002</t>
+          <t>133142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59477</t>
+          <t>59978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78426</t>
+          <t>78507</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67622</t>
+          <t>67778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89703</t>
+          <t>89001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132845</t>
+          <t>132341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161366</t>
+          <t>160819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73501</t>
+          <t>73420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92450</t>
+          <t>91949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>85600</t>
+          <t>86302</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107681</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165864</t>
+          <t>166411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194385</t>
+          <t>194889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>35190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51169</t>
+          <t>51338</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47099</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65641</t>
+          <t>65363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88277</t>
+          <t>88092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112399</t>
+          <t>111541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65383</t>
+          <t>65214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81310</t>
+          <t>81362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67206</t>
+          <t>67484</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85748</t>
+          <t>85694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137000</t>
+          <t>137858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161122</t>
+          <t>161307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,68%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67722</t>
+          <t>65851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89462</t>
+          <t>88318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49449</t>
+          <t>49591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69764</t>
+          <t>69989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122804</t>
+          <t>122746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152654</t>
+          <t>153613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,26%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77365</t>
+          <t>78509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99105</t>
+          <t>100976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88444</t>
+          <t>88219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108759</t>
+          <t>108617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172381</t>
+          <t>171422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202231</t>
+          <t>202289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205187</t>
+          <t>206228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>245939</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>216460</t>
+          <t>214222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>254440</t>
+          <t>253416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>429534</t>
+          <t>430455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>483422</t>
+          <t>483498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>279451</t>
+          <t>284284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320203</t>
+          <t>319162</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>316593</t>
+          <t>317617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>354573</t>
+          <t>356811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>613001</t>
+          <t>612925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>666889</t>
+          <t>665968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107567</t>
+          <t>107971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114389</t>
+          <t>114675</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128687</t>
+          <t>128309</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138344</t>
+          <t>138310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>240555</t>
+          <t>239905</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251480</t>
+          <t>251698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17138</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177345</t>
+          <t>177362</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>186318</t>
+          <t>186349</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>230995</t>
+          <t>232302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>247227</t>
+          <t>246963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>413272</t>
+          <t>412465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>431216</t>
+          <t>431649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>22733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>33083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>176373</t>
+          <t>175334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186513</t>
+          <t>186304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166612</t>
+          <t>165963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178559</t>
+          <t>177971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>347047</t>
+          <t>347359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>362966</t>
+          <t>362578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>15067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28640</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149413</t>
+          <t>149939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161149</t>
+          <t>162139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>165529</t>
+          <t>166776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177043</t>
+          <t>176969</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>320023</t>
+          <t>320060</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>335823</t>
+          <t>336001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29178</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>623857</t>
+          <t>624388</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>643158</t>
+          <t>642736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>708305</t>
+          <t>709120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>732249</t>
+          <t>732502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1339500</t>
+          <t>1340125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1368932</t>
+          <t>1370764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42298</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>57363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88627</t>
+          <t>88002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49766</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41504</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59300</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,07%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>35,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>39335</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31830</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47647</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31465</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48086</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,39%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>49766</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>40535</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59378</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,07%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78001</t>
+          <t>76712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101065</t>
+          <t>101435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68523</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58989</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76785</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>65874</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57562</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73379</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>57123</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73744</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>62,61%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>54,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68523</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58911</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77754</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>57,93%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122434</t>
+          <t>122064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145498</t>
+          <t>146787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58073</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>48424</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67801</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>47853</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39986</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56603</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>40027</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57110</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>38,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>58073</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>49753</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67909</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,26%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93848</t>
+          <t>94584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119044</t>
+          <t>120133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82669</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72941</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92318</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>77112</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68362</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>84979</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>67855</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>84938</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>61,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>68,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>82669</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72833</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>90989</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>58,74%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146663</t>
+          <t>145574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171859</t>
+          <t>171123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52737</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44378</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61387</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,85%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>45742</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37639</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53939</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37814</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>53985</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>42,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>52737</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>44567</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>60331</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>46,85%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86939</t>
+          <t>88274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109781</t>
+          <t>109651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>59836</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>51186</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>68195</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>53,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>62106</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53909</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>70209</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53863</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>70034</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>57,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>59836</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52242</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>68006</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>53,15%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110639</t>
+          <t>110769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>133481</t>
+          <t>132146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>65657</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56023</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>76657</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>67215</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>56927</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>79160</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>56565</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>78916</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>40,65%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>47,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>65657</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>55226</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>75176</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118548</t>
+          <t>118643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146690</t>
+          <t>147022</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91289</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80289</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>100923</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>98121</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>86176</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>108409</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>86420</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>108771</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,35%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>52,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>91289</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>81770</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>101720</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175592</t>
+          <t>175260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>203734</t>
+          <t>203639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>208384</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>245623</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>200145</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>181145</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>217000</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>181684</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>218077</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>39,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>226233</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>208778</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>245146</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>399580</t>
+          <t>400649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>453282</t>
+          <t>450187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>302316</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>282926</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>320165</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>57,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>53,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>60,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>450</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>303214</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>286359</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>322214</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>285282</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>321675</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>60,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>56,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>64,01%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>302316</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>283403</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>319771</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>57,2%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>578626</t>
+          <t>581721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>632328</t>
+          <t>631259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>56308</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48226</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65029</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>45627</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37410</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>55236</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>37980</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>53922</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,98%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>56308</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>47880</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>65466</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89991</t>
+          <t>89999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113616</t>
+          <t>113791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56193</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47472</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64275</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51502</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41893</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43207</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>59149</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>53,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>61,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56193</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47035</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>64621</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,95%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96013</t>
+          <t>95838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119638</t>
+          <t>119630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77801</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68069</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>88309</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>50,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>44,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>66041</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>57306</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>75299</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>56595</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>74868</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>51,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>44,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>77801</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67637</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>87409</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130428</t>
+          <t>130126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156402</t>
+          <t>156067</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>76755</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>66247</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>86487</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>49,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>55,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>62942</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>53684</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>71677</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>54115</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72388</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>48,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,62%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>55,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>76755</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>67147</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>86919</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>49,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127137</t>
+          <t>127472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153111</t>
+          <t>153413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54699</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46128</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>62899</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>46,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>53,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>48307</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40651</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56210</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>39977</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56281</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>46,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>54699</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>46677</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>64233</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>46,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91134</t>
+          <t>92048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114824</t>
+          <t>115040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62085</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53885</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>70656</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>53,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>56544</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48641</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>64200</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>48570</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>64874</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>53,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>61,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>62085</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52551</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>70107</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>53,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106810</t>
+          <t>106594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130500</t>
+          <t>129586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>70265</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60648</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>81325</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>62419</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>52606</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>72875</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52652</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>72757</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>42,75%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,91%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>70265</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>59700</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>80992</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>45,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118683</t>
+          <t>117974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146795</t>
+          <t>147027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>84676</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>73616</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94293</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>83583</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73127</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>93396</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>73245</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>93350</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>57,25%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,09%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>84676</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>73949</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>95241</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154148</t>
+          <t>153916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182260</t>
+          <t>182969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>238688</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>276489</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>320</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>222394</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>204644</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>239956</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>205485</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>239569</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>46,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>259073</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>240217</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>278303</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>454476</t>
+          <t>455074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>506927</t>
+          <t>505661</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>279708</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>262292</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>300093</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>254571</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>237009</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>272321</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>237396</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>271480</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>53,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,09%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>279708</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>260478</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>298564</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>51,92%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>508819</t>
+          <t>510085</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>561270</t>
+          <t>560672</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>41150</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33168</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49415</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>31755</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24955</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40284</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24017</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39356</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>35,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>41150</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33147</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>51089</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,31%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61617</t>
+          <t>61270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84072</t>
+          <t>85451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63524</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55259</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71506</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>52,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>68,31%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>58330</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49801</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>65130</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50729</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66068</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>64,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63524</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53585</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>71527</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>60,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110687</t>
+          <t>109308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133142</t>
+          <t>133489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77990</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>67573</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>88767</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>44,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>69312</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>59978</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>78507</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>59358</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>78784</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>45,62%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39,48%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>77990</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67778</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>89001</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>44,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132341</t>
+          <t>133130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160819</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>97313</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86536</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>107730</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>55,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>82615</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73420</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91949</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>73143</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>92569</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>54,38%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>97313</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>86302</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>107525</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>55,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>166411</t>
+          <t>165399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194889</t>
+          <t>194100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56216</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45852</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64357</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>43630</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35190</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51338</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>36169</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>51912</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>37,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>56216</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>47153</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>65363</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,32%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88092</t>
+          <t>88091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111541</t>
+          <t>111578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76631</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68490</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86995</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,56%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72922</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65214</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>81362</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64640</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>80383</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>62,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76631</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67484</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>85694</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>57,68%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137858</t>
+          <t>137821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161307</t>
+          <t>161308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59262</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50142</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69818</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,46%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>77977</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65851</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>88318</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>67586</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>46,74%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>59262</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>49591</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>69989</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,46%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122746</t>
+          <t>122679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153613</t>
+          <t>151868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98946</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>88390</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>108066</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>88850</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>78509</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>100976</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>77064</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>99241</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98946</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>88219</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>108617</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,54%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171422</t>
+          <t>173167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>202289</t>
+          <t>202356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,26%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>216293</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>255101</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>222674</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>206228</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>241106</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>204609</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>239933</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>234618</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>214222</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>253416</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>430455</t>
+          <t>431014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>483498</t>
+          <t>485340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>336415</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>315932</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>354740</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>55,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>62,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>302716</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>284284</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>319162</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>285457</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>320781</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>57,62%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>54,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>60,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>336415</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>317617</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>356811</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>612925</t>
+          <t>611083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>665968</t>
+          <t>665409</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,69%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>121366</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>113387</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>123801</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>90,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>111992</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>107971</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>114675</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>135087</t>
+          <t>115971</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128309</t>
+          <t>111636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138310</t>
+          <t>118568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>247080</t>
+          <t>237338</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239905</t>
+          <t>230311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251698</t>
+          <t>241332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4540</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12519</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9309</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10613</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>224179</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>216189</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>229845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>91,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>182854</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>177362</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>186349</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>241013</t>
+          <t>177475</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>232302</t>
+          <t>172210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246963</t>
+          <t>180989</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,27 +6982,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>423869</t>
+          <t>401654</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>412465</t>
+          <t>392219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>431649</t>
+          <t>408484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13027</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7361</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21017</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7658</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4163</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13150</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22733</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,22 +7095,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>13135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>157707</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>151261</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>162127</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>182173</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>175334</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>186304</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>173656</t>
+          <t>148579</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165963</t>
+          <t>142400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177971</t>
+          <t>152403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>355829</t>
+          <t>306286</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>347359</t>
+          <t>296989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>362578</t>
+          <t>312088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10634</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6214</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>17080</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8228</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15067</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>160945</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>154934</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>165014</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>156648</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>149939</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>162139</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>89,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>172412</t>
+          <t>155454</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166776</t>
+          <t>148564</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176969</t>
+          <t>160634</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>329061</t>
+          <t>316398</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>320060</t>
+          <t>307892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336001</t>
+          <t>323093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8431</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14442</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11314</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5823</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18023</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20140</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>664197</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>651951</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>673502</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>93,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>893</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>633667</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>624388</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>642736</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>597478</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>709120</t>
+          <t>586887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>732502</t>
+          <t>605754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1355836</t>
+          <t>1261676</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1340125</t>
+          <t>1246306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1370764</t>
+          <t>1274903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36632</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27327</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>48878</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>32488</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>23419</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>41767</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29470</t>
+          <t>23924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52852</t>
+          <t>42791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>68832</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57363</t>
+          <t>55605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88002</t>
+          <t>84202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
